--- a/artfynd/A 19500-2024 artfynd.xlsx
+++ b/artfynd/A 19500-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136250576</v>
       </c>
       <c r="B2" t="n">
-        <v>105785</v>
+        <v>105788</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136250581</v>
       </c>
       <c r="B3" t="n">
-        <v>106517</v>
+        <v>106520</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19500-2024 artfynd.xlsx
+++ b/artfynd/A 19500-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136250576</v>
       </c>
       <c r="B2" t="n">
-        <v>105788</v>
+        <v>105789</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136250581</v>
       </c>
       <c r="B3" t="n">
-        <v>106520</v>
+        <v>106521</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19500-2024 artfynd.xlsx
+++ b/artfynd/A 19500-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136250576</v>
       </c>
       <c r="B2" t="n">
-        <v>105789</v>
+        <v>105794</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136250581</v>
       </c>
       <c r="B3" t="n">
-        <v>106521</v>
+        <v>106526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19500-2024 artfynd.xlsx
+++ b/artfynd/A 19500-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136250576</v>
       </c>
       <c r="B2" t="n">
-        <v>105794</v>
+        <v>105796</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136250581</v>
       </c>
       <c r="B3" t="n">
-        <v>106526</v>
+        <v>106528</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
